--- a/Cuentas bancos.xlsx
+++ b/Cuentas bancos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Otros ordenadores\Mi portátil\Desktop\Conciliacion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9509BD6F-A1FC-44DC-8E1D-25F98CCA9FC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96CDC5CD-CC4D-41D2-8975-BB41C0B21B97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{52D0CD0F-A890-48B3-9ED9-E87DCFAC9521}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="40">
   <si>
     <t>CUENTA</t>
   </si>
@@ -127,6 +127,24 @@
   </si>
   <si>
     <t>CUENTA MAYOR</t>
+  </si>
+  <si>
+    <t>11100501</t>
+  </si>
+  <si>
+    <t>11100511</t>
+  </si>
+  <si>
+    <t>11100531</t>
+  </si>
+  <si>
+    <t>11100541</t>
+  </si>
+  <si>
+    <t>11100571</t>
+  </si>
+  <si>
+    <t>11200511</t>
   </si>
 </sst>
 </file>
@@ -215,7 +233,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -224,9 +242,17 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -541,15 +567,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A6E770B-9C2F-4AA0-B21B-848A2F44D913}">
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
+    <col min="1" max="1" width="10.90625" style="6"/>
+    <col min="2" max="2" width="23.453125" customWidth="1"/>
     <col min="4" max="4" width="14.08984375" customWidth="1"/>
     <col min="5" max="5" width="20.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="4" t="s">
         <v>33</v>
       </c>
       <c r="B1" s="1" t="s">
@@ -566,7 +594,7 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A2" s="4">
+      <c r="A2" s="5">
         <v>11100591</v>
       </c>
       <c r="B2" s="3" t="s">
@@ -583,7 +611,7 @@
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A3" s="4">
+      <c r="A3" s="5">
         <v>11100501</v>
       </c>
       <c r="B3" s="3" t="s">
@@ -600,7 +628,7 @@
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A4" s="4">
+      <c r="A4" s="5">
         <v>11100511</v>
       </c>
       <c r="B4" s="3" t="s">
@@ -617,7 +645,7 @@
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A5" s="4">
+      <c r="A5" s="5">
         <v>11100571</v>
       </c>
       <c r="B5" s="3" t="s">
@@ -634,7 +662,7 @@
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A6" s="4">
+      <c r="A6" s="5">
         <v>11100581</v>
       </c>
       <c r="B6" s="3" t="s">
@@ -651,7 +679,7 @@
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A7" s="4">
+      <c r="A7" s="5">
         <v>11200511</v>
       </c>
       <c r="B7" s="3" t="s">
@@ -668,7 +696,7 @@
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A8" s="4">
+      <c r="A8" s="5">
         <v>11100541</v>
       </c>
       <c r="B8" s="3" t="s">
@@ -685,7 +713,7 @@
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A9" s="4">
+      <c r="A9" s="5">
         <v>12450201</v>
       </c>
       <c r="B9" s="3" t="s">
@@ -702,7 +730,7 @@
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A10" s="4">
+      <c r="A10" s="5">
         <v>11100531</v>
       </c>
       <c r="B10" s="3" t="s">
@@ -719,7 +747,7 @@
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A11" s="4">
+      <c r="A11" s="5">
         <v>11200501</v>
       </c>
       <c r="B11" s="3" t="s">
@@ -736,7 +764,7 @@
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A12" s="4">
+      <c r="A12" s="5">
         <v>11100561</v>
       </c>
       <c r="B12" s="3" t="s">
@@ -753,7 +781,7 @@
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A13" s="4">
+      <c r="A13" s="5">
         <v>11100521</v>
       </c>
       <c r="B13" s="3" t="s">
@@ -770,7 +798,7 @@
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A14" s="4">
+      <c r="A14" s="5">
         <v>11100551</v>
       </c>
       <c r="B14" s="3" t="s">
@@ -787,7 +815,7 @@
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A15" s="4">
+      <c r="A15" s="5">
         <v>11200601</v>
       </c>
       <c r="B15" s="3" t="s">
@@ -801,6 +829,132 @@
       </c>
       <c r="E15" s="3" t="s">
         <v>18</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A16" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B16" s="8" t="str">
+        <f ca="1">VLOOKUP(A16,Hoja1!$A:$E,2,0)</f>
+        <v>BANCOLOMBIA0616</v>
+      </c>
+      <c r="C16" s="8" t="str">
+        <f ca="1">VLOOKUP(A16,Hoja1!$A:$E,3,0)</f>
+        <v>CA</v>
+      </c>
+      <c r="D16" s="8" t="str">
+        <f ca="1">VLOOKUP(A16,Hoja1!$A:$E,4,0)</f>
+        <v>BANCOLOMBIA</v>
+      </c>
+      <c r="E16" s="8" t="str">
+        <f ca="1">VLOOKUP(A16,Hoja1!$A:$E,5,0)</f>
+        <v>Consignaciones/Cartera</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A17" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="B17" s="8" t="str">
+        <f ca="1">VLOOKUP(A17,Hoja1!$A:$E,2,0)</f>
+        <v>BANCOLOMBIA6774</v>
+      </c>
+      <c r="C17" s="8" t="str">
+        <f ca="1">VLOOKUP(A17,Hoja1!$A:$E,3,0)</f>
+        <v>CA</v>
+      </c>
+      <c r="D17" s="8" t="str">
+        <f ca="1">VLOOKUP(A17,Hoja1!$A:$E,4,0)</f>
+        <v>BANCOLOMBIA</v>
+      </c>
+      <c r="E17" s="8" t="str">
+        <f ca="1">VLOOKUP(A17,Hoja1!$A:$E,5,0)</f>
+        <v>Consignaciones/Cartera</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A18" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="B18" s="8" t="str">
+        <f ca="1">VLOOKUP(A18,Hoja1!$A:$E,2,0)</f>
+        <v>ITAU3956</v>
+      </c>
+      <c r="C18" s="8" t="str">
+        <f ca="1">VLOOKUP(A18,Hoja1!$A:$E,3,0)</f>
+        <v>CA</v>
+      </c>
+      <c r="D18" s="8" t="str">
+        <f ca="1">VLOOKUP(A18,Hoja1!$A:$E,4,0)</f>
+        <v>ITAU</v>
+      </c>
+      <c r="E18" s="8" t="str">
+        <f ca="1">VLOOKUP(A18,Hoja1!$A:$E,5,0)</f>
+        <v>Cartera</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A19" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B19" s="8" t="str">
+        <f ca="1">VLOOKUP(A19,Hoja1!$A:$E,2,0)</f>
+        <v>DAVIVIENDA8744</v>
+      </c>
+      <c r="C19" s="8" t="str">
+        <f ca="1">VLOOKUP(A19,Hoja1!$A:$E,3,0)</f>
+        <v>CA</v>
+      </c>
+      <c r="D19" s="8" t="str">
+        <f ca="1">VLOOKUP(A19,Hoja1!$A:$E,4,0)</f>
+        <v>DAVIVIENDA</v>
+      </c>
+      <c r="E19" s="8" t="str">
+        <f ca="1">VLOOKUP(A19,Hoja1!$A:$E,5,0)</f>
+        <v>Consignaciones</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A20" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B20" s="8" t="str">
+        <f ca="1">VLOOKUP(A20,Hoja1!$A:$E,2,0)</f>
+        <v>BBVA1730</v>
+      </c>
+      <c r="C20" s="8" t="str">
+        <f ca="1">VLOOKUP(A20,Hoja1!$A:$E,3,0)</f>
+        <v>CA</v>
+      </c>
+      <c r="D20" s="8" t="str">
+        <f ca="1">VLOOKUP(A20,Hoja1!$A:$E,4,0)</f>
+        <v>BBVA</v>
+      </c>
+      <c r="E20" s="8" t="str">
+        <f ca="1">VLOOKUP(A20,Hoja1!$A:$E,5,0)</f>
+        <v>Cartera</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A21" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B21" s="8" t="str">
+        <f ca="1">VLOOKUP(A21,Hoja1!$A:$E,2,0)</f>
+        <v>DAVIVIENDA6100</v>
+      </c>
+      <c r="C21" s="8" t="str">
+        <f ca="1">VLOOKUP(A21,Hoja1!$A:$E,3,0)</f>
+        <v>CA</v>
+      </c>
+      <c r="D21" s="8" t="str">
+        <f ca="1">VLOOKUP(A21,Hoja1!$A:$E,4,0)</f>
+        <v>DAVIVIENDA</v>
+      </c>
+      <c r="E21" s="8" t="str">
+        <f ca="1">VLOOKUP(A21,Hoja1!$A:$E,5,0)</f>
+        <v>Datafonos</v>
       </c>
     </row>
   </sheetData>
